--- a/artfynd/A 7891-2022 artfynd.xlsx
+++ b/artfynd/A 7891-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7891-2022 artfynd.xlsx
+++ b/artfynd/A 7891-2022 artfynd.xlsx
@@ -675,52 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102572006</v>
+        <v>102571921</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hoverberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472006.0492864912</v>
+        <v>472007</v>
       </c>
       <c r="R2" t="n">
-        <v>6965787.300090424</v>
+        <v>6965787</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,19 +744,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,52 +773,55 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102572300</v>
+        <v>102572250</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Berg, Jmt</t>
+          <t>Hoverberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472010.233985626</v>
+        <v>471997</v>
       </c>
       <c r="R3" t="n">
-        <v>6965848.525759418</v>
+        <v>6965861</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +851,14 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Avverkningsanmäld skog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,12 +888,7 @@
         <v>102571869</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472007.549044116</v>
+        <v>472008</v>
       </c>
       <c r="R4" t="n">
-        <v>6965748.426891573</v>
+        <v>6965748</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,19 +955,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,51 +984,47 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102571921</v>
+        <v>102572300</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hoverberget, Jmt</t>
+          <t>Berg, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472006.0492864912</v>
+        <v>472011</v>
       </c>
       <c r="R5" t="n">
-        <v>6965787.300090424</v>
+        <v>6965849</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,19 +1054,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,60 +1083,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102572250</v>
+        <v>102572370</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hoverberget, Jmt</t>
+          <t>Berg, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471996.1481300473</v>
+        <v>472010</v>
       </c>
       <c r="R6" t="n">
-        <v>6965860.989482025</v>
+        <v>6965839</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,24 +1153,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Avverkningsanmäld skog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,15 +1182,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102572370</v>
+        <v>102572006</v>
       </c>
       <c r="B7" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,21 +1193,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,14 +1215,14 @@
       <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Berg, Jmt</t>
+          <t>Hoverberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472009.6982359469</v>
+        <v>472007</v>
       </c>
       <c r="R7" t="n">
-        <v>6965839.386914443</v>
+        <v>6965787</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1332,19 +1252,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 7891-2022 artfynd.xlsx
+++ b/artfynd/A 7891-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102571921</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102572250</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102571869</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102572300</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102572370</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,8 +1308,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102572006</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>